--- a/data/output/Planilha Resultado.xlsx
+++ b/data/output/Planilha Resultado.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -55,11 +58,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I63"/>
+  <dimension ref="A1:J63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,22 +440,22 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>CPF</t>
+          <t>Departamento</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Departamento</t>
+          <t>Salario</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Salario</t>
+          <t>Gympass</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Gympass</t>
+          <t>Código</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -466,10 +470,15 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>Data Ativacao</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>Github</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
@@ -483,19 +492,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>398.122.745-XX</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>R&amp;D</t>
-        </is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>3384.960765580439</v>
       </c>
       <c r="D2" t="n">
-        <v>3384.960765580439</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>90</v>
+        <v>82289354</v>
       </c>
       <c r="F2" t="n">
         <v>533.99</v>
@@ -503,11 +510,14 @@
       <c r="G2" t="n">
         <v>297.13</v>
       </c>
-      <c r="H2" t="n">
+      <c r="H2" s="2" t="n">
+        <v>45071</v>
+      </c>
+      <c r="I2" t="n">
         <v>254.63</v>
       </c>
-      <c r="I2" t="n">
-        <v>4560.710765580439</v>
+      <c r="J2" t="n">
+        <v>4470.710765580439</v>
       </c>
     </row>
     <row r="3">
@@ -518,19 +528,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>107.885.329-XX</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>R&amp;D</t>
-        </is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>3719.103451680459</v>
       </c>
       <c r="D3" t="n">
-        <v>3719.103451680459</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>90</v>
+        <v>82289359</v>
       </c>
       <c r="F3" t="n">
         <v>855.8</v>
@@ -538,11 +546,14 @@
       <c r="G3" t="n">
         <v>297.13</v>
       </c>
-      <c r="H3" t="n">
-        <v>0</v>
+      <c r="H3" s="2" t="n">
+        <v>44693</v>
       </c>
       <c r="I3" t="n">
-        <v>4962.033451680459</v>
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>4872.033451680459</v>
       </c>
     </row>
     <row r="4">
@@ -553,19 +564,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>432.976.108-XX</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
           <t>G&amp;A</t>
         </is>
       </c>
+      <c r="C4" t="n">
+        <v>8962.729721841501</v>
+      </c>
       <c r="D4" t="n">
-        <v>8962.729721841501</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>90</v>
+        <v>82289363</v>
       </c>
       <c r="F4" t="n">
         <v>444.99</v>
@@ -573,11 +582,14 @@
       <c r="G4" t="n">
         <v>297.13</v>
       </c>
-      <c r="H4" t="n">
+      <c r="H4" s="2" t="n">
+        <v>45485</v>
+      </c>
+      <c r="I4" t="n">
         <v>141.46</v>
       </c>
-      <c r="I4" t="n">
-        <v>9936.309721841499</v>
+      <c r="J4" t="n">
+        <v>9846.309721841499</v>
       </c>
     </row>
     <row r="5">
@@ -588,19 +600,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>215.630.874-XX</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>R&amp;D</t>
-        </is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>8059.789738823023</v>
       </c>
       <c r="D5" t="n">
-        <v>8059.789738823023</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>90</v>
+        <v>82289366</v>
       </c>
       <c r="F5" t="n">
         <v>444.99</v>
@@ -608,11 +618,14 @@
       <c r="G5" t="n">
         <v>297.13</v>
       </c>
-      <c r="H5" t="n">
-        <v>0</v>
+      <c r="H5" s="2" t="n">
+        <v>45386</v>
       </c>
       <c r="I5" t="n">
-        <v>8891.909738823022</v>
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>8801.909738823022</v>
       </c>
     </row>
     <row r="6">
@@ -623,19 +636,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>569.041.233-XX</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>R&amp;D</t>
-        </is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>7364.526801321949</v>
       </c>
       <c r="D6" t="n">
-        <v>7364.526801321949</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>90</v>
+        <v>82289369</v>
       </c>
       <c r="F6" t="n">
         <v>444.99</v>
@@ -643,11 +654,14 @@
       <c r="G6" t="n">
         <v>297.13</v>
       </c>
-      <c r="H6" t="n">
-        <v>0</v>
+      <c r="H6" s="2" t="n">
+        <v>45163</v>
       </c>
       <c r="I6" t="n">
-        <v>8196.646801321949</v>
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>8106.646801321949</v>
       </c>
     </row>
     <row r="7">
@@ -658,19 +672,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>088.714.596-XX</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>R&amp;D</t>
-        </is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>5318.987724937523</v>
       </c>
       <c r="D7" t="n">
-        <v>5318.987724937523</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>90</v>
+        <v>82289371</v>
       </c>
       <c r="F7" t="n">
         <v>444.99</v>
@@ -678,11 +690,14 @@
       <c r="G7" t="n">
         <v>297.13</v>
       </c>
-      <c r="H7" t="n">
-        <v>0</v>
+      <c r="H7" s="2" t="n">
+        <v>45645</v>
       </c>
       <c r="I7" t="n">
-        <v>6151.107724937523</v>
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>6061.107724937523</v>
       </c>
     </row>
     <row r="8">
@@ -693,19 +708,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>321.458.907-XX</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>R&amp;D</t>
-        </is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>9551.21905794158</v>
       </c>
       <c r="D8" t="n">
-        <v>9551.21905794158</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>90</v>
+        <v>82381757</v>
       </c>
       <c r="F8" t="n">
         <v>364.76</v>
@@ -713,11 +726,14 @@
       <c r="G8" t="n">
         <v>297.13</v>
       </c>
-      <c r="H8" t="n">
+      <c r="H8" s="2" t="n">
+        <v>45069</v>
+      </c>
+      <c r="I8" t="n">
         <v>254.63</v>
       </c>
-      <c r="I8" t="n">
-        <v>10557.73905794158</v>
+      <c r="J8" t="n">
+        <v>10467.73905794158</v>
       </c>
     </row>
     <row r="9">
@@ -728,19 +744,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>654.102.385-XX</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
           <t>G&amp;A</t>
         </is>
       </c>
+      <c r="C9" t="n">
+        <v>8284.136836853117</v>
+      </c>
       <c r="D9" t="n">
-        <v>8284.136836853117</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>90</v>
+        <v>83512049</v>
       </c>
       <c r="F9" t="n">
         <v>560.7</v>
@@ -748,11 +762,14 @@
       <c r="G9" t="n">
         <v>297.13</v>
       </c>
-      <c r="H9" t="n">
+      <c r="H9" s="2" t="n">
+        <v>45554</v>
+      </c>
+      <c r="I9" t="n">
         <v>254.63</v>
       </c>
-      <c r="I9" t="n">
-        <v>9486.596836853116</v>
+      <c r="J9" t="n">
+        <v>9396.596836853116</v>
       </c>
     </row>
     <row r="10">
@@ -763,19 +780,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>987.546.721-XX</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>R&amp;D</t>
-        </is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>1315.118209620667</v>
       </c>
       <c r="D10" t="n">
-        <v>1315.118209620667</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>90</v>
+        <v>83685992</v>
       </c>
       <c r="F10" t="n">
         <v>444.99</v>
@@ -783,11 +798,14 @@
       <c r="G10" t="n">
         <v>297.13</v>
       </c>
-      <c r="H10" t="n">
+      <c r="H10" s="2" t="n">
+        <v>45405</v>
+      </c>
+      <c r="I10" t="n">
         <v>254.63</v>
       </c>
-      <c r="I10" t="n">
-        <v>2401.868209620667</v>
+      <c r="J10" t="n">
+        <v>2311.868209620667</v>
       </c>
     </row>
     <row r="11">
@@ -798,19 +816,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>851.304.270-XX</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>R&amp;D</t>
-        </is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>4021.833629163991</v>
       </c>
       <c r="D11" t="n">
-        <v>4021.833629163991</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>90</v>
+        <v>83983414</v>
       </c>
       <c r="F11" t="n">
         <v>848.05</v>
@@ -818,11 +834,14 @@
       <c r="G11" t="n">
         <v>297.13</v>
       </c>
-      <c r="H11" t="n">
-        <v>0</v>
+      <c r="H11" s="2" t="n">
+        <v>45628</v>
       </c>
       <c r="I11" t="n">
-        <v>5257.013629163992</v>
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>5167.013629163991</v>
       </c>
     </row>
     <row r="12">
@@ -833,19 +852,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>162.415.381-XX</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>R&amp;D</t>
-        </is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>5244.623025188975</v>
       </c>
       <c r="D12" t="n">
-        <v>5244.623025188975</v>
+        <v>27</v>
       </c>
       <c r="E12" t="n">
-        <v>117</v>
+        <v>84023403</v>
       </c>
       <c r="F12" t="n">
         <v>533.99</v>
@@ -853,11 +870,14 @@
       <c r="G12" t="n">
         <v>297.13</v>
       </c>
-      <c r="H12" t="n">
-        <v>0</v>
+      <c r="H12" s="2" t="n">
+        <v>44693</v>
       </c>
       <c r="I12" t="n">
-        <v>6192.743025188975</v>
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>6102.743025188975</v>
       </c>
     </row>
     <row r="13">
@@ -868,19 +888,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>273.526.492-XX</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>R&amp;D</t>
-        </is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>8057.257421621038</v>
       </c>
       <c r="D13" t="n">
-        <v>8057.257421621038</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>90</v>
+        <v>84124781</v>
       </c>
       <c r="F13" t="n">
         <v>444.99</v>
@@ -888,11 +906,14 @@
       <c r="G13" t="n">
         <v>297.13</v>
       </c>
-      <c r="H13" t="n">
-        <v>0</v>
+      <c r="H13" s="2" t="n">
+        <v>44693</v>
       </c>
       <c r="I13" t="n">
-        <v>8889.377421621037</v>
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>8799.377421621037</v>
       </c>
     </row>
     <row r="14">
@@ -903,19 +924,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>594.637.503-XX</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
           <t>G&amp;A</t>
         </is>
       </c>
+      <c r="C14" t="n">
+        <v>9712.728285382607</v>
+      </c>
       <c r="D14" t="n">
-        <v>9712.728285382607</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>90</v>
+        <v>84124815</v>
       </c>
       <c r="F14" t="n">
         <v>533.99</v>
@@ -923,11 +942,14 @@
       <c r="G14" t="n">
         <v>297.13</v>
       </c>
-      <c r="H14" t="n">
+      <c r="H14" s="2" t="n">
+        <v>45677</v>
+      </c>
+      <c r="I14" t="n">
         <v>141.46</v>
       </c>
-      <c r="I14" t="n">
-        <v>10775.30828538261</v>
+      <c r="J14" t="n">
+        <v>10685.30828538261</v>
       </c>
     </row>
     <row r="15">
@@ -938,19 +960,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>426.859.725-XX</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>R&amp;D</t>
-        </is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>8029.53768092652</v>
       </c>
       <c r="D15" t="n">
-        <v>8029.53768092652</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>90</v>
+        <v>84434718</v>
       </c>
       <c r="F15" t="n">
         <v>444.99</v>
@@ -958,11 +978,14 @@
       <c r="G15" t="n">
         <v>297.13</v>
       </c>
-      <c r="H15" t="n">
+      <c r="H15" s="2" t="n">
+        <v>45684</v>
+      </c>
+      <c r="I15" t="n">
         <v>141.46</v>
       </c>
-      <c r="I15" t="n">
-        <v>9003.117680926518</v>
+      <c r="J15" t="n">
+        <v>8913.117680926518</v>
       </c>
     </row>
     <row r="16">
@@ -973,19 +996,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>015.748.614-XX</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>R&amp;D</t>
-        </is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>7487.999892436921</v>
       </c>
       <c r="D16" t="n">
-        <v>7487.999892436921</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>90</v>
+        <v>84177072</v>
       </c>
       <c r="F16" t="n">
         <v>533.99</v>
@@ -993,11 +1014,14 @@
       <c r="G16" t="n">
         <v>297.13</v>
       </c>
-      <c r="H16" t="n">
+      <c r="H16" s="2" t="n">
+        <v>44778</v>
+      </c>
+      <c r="I16" t="n">
         <v>141.46</v>
       </c>
-      <c r="I16" t="n">
-        <v>8550.579892436919</v>
+      <c r="J16" t="n">
+        <v>8460.579892436919</v>
       </c>
     </row>
     <row r="17">
@@ -1008,19 +1032,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>868.071.947-XX</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>R&amp;D</t>
-        </is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>1108.340345861018</v>
       </c>
       <c r="D17" t="n">
-        <v>1108.340345861018</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>90</v>
+        <v>85068324</v>
       </c>
       <c r="F17" t="n">
         <v>444.99</v>
@@ -1028,11 +1050,14 @@
       <c r="G17" t="n">
         <v>297.13</v>
       </c>
-      <c r="H17" t="n">
-        <v>0</v>
+      <c r="H17" s="2" t="n">
+        <v>45646</v>
       </c>
       <c r="I17" t="n">
-        <v>1940.460345861018</v>
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1850.460345861018</v>
       </c>
     </row>
     <row r="18">
@@ -1043,19 +1068,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>179.182.058-XX</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>R&amp;D</t>
-        </is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>9976.53102463056</v>
       </c>
       <c r="D18" t="n">
-        <v>9976.53102463056</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>90</v>
+        <v>85099819</v>
       </c>
       <c r="F18" t="n">
         <v>444.99</v>
@@ -1063,11 +1086,14 @@
       <c r="G18" t="n">
         <v>297.13</v>
       </c>
-      <c r="H18" t="n">
+      <c r="H18" s="2" t="n">
+        <v>45655</v>
+      </c>
+      <c r="I18" t="n">
         <v>254.63</v>
       </c>
-      <c r="I18" t="n">
-        <v>11063.28102463056</v>
+      <c r="J18" t="n">
+        <v>10973.28102463056</v>
       </c>
     </row>
     <row r="19">
@@ -1078,19 +1104,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>500.293.169-XX</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>R&amp;D</t>
-        </is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>3295.032751492262</v>
       </c>
       <c r="D19" t="n">
-        <v>3295.032751492262</v>
+        <v>27</v>
       </c>
       <c r="E19" t="n">
-        <v>117</v>
+        <v>86365385</v>
       </c>
       <c r="F19" t="n">
         <v>560.7</v>
@@ -1098,11 +1122,14 @@
       <c r="G19" t="n">
         <v>297.13</v>
       </c>
-      <c r="H19" t="n">
+      <c r="H19" s="2" t="n">
+        <v>44693</v>
+      </c>
+      <c r="I19" t="n">
         <v>254.63</v>
       </c>
-      <c r="I19" t="n">
-        <v>4524.492751492262</v>
+      <c r="J19" t="n">
+        <v>4434.492751492262</v>
       </c>
     </row>
     <row r="20">
@@ -1113,19 +1140,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>291.304.270-XX</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
           <t>COGS</t>
         </is>
       </c>
+      <c r="C20" t="n">
+        <v>8271.84079484528</v>
+      </c>
       <c r="D20" t="n">
-        <v>8271.84079484528</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>90</v>
+        <v>86636130</v>
       </c>
       <c r="F20" t="n">
         <v>533.99</v>
@@ -1133,11 +1158,14 @@
       <c r="G20" t="n">
         <v>297.13</v>
       </c>
-      <c r="H20" t="n">
+      <c r="H20" s="2" t="n">
+        <v>44708</v>
+      </c>
+      <c r="I20" t="n">
         <v>254.63</v>
       </c>
-      <c r="I20" t="n">
-        <v>9447.590794845279</v>
+      <c r="J20" t="n">
+        <v>9357.590794845279</v>
       </c>
     </row>
     <row r="21">
@@ -1148,19 +1176,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>612.415.381-XX</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
           <t>COGS</t>
         </is>
       </c>
+      <c r="C21" t="n">
+        <v>5288.260196934793</v>
+      </c>
       <c r="D21" t="n">
-        <v>5288.260196934793</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>90</v>
+        <v>87937128</v>
       </c>
       <c r="F21" t="n">
         <v>444.99</v>
@@ -1168,11 +1194,14 @@
       <c r="G21" t="n">
         <v>297.13</v>
       </c>
-      <c r="H21" t="n">
-        <v>0</v>
+      <c r="H21" s="2" t="n">
+        <v>44770</v>
       </c>
       <c r="I21" t="n">
-        <v>6120.380196934793</v>
+        <v>0</v>
+      </c>
+      <c r="J21" t="n">
+        <v>6030.380196934793</v>
       </c>
     </row>
     <row r="22">
@@ -1183,19 +1212,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>933.526.492-XX</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>R&amp;D</t>
-        </is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>4963.54282637831</v>
       </c>
       <c r="D22" t="n">
-        <v>4963.54282637831</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>90</v>
+        <v>87945092</v>
       </c>
       <c r="F22" t="n">
         <v>560.7</v>
@@ -1203,11 +1230,14 @@
       <c r="G22" t="n">
         <v>297.13</v>
       </c>
-      <c r="H22" t="n">
+      <c r="H22" s="2" t="n">
+        <v>44852</v>
+      </c>
+      <c r="I22" t="n">
         <v>254.63</v>
       </c>
-      <c r="I22" t="n">
-        <v>6166.00282637831</v>
+      <c r="J22" t="n">
+        <v>6076.00282637831</v>
       </c>
     </row>
     <row r="23">
@@ -1218,19 +1248,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>675.748.614-XX</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>R&amp;D</t>
-        </is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>3230.18657849905</v>
       </c>
       <c r="D23" t="n">
-        <v>3230.18657849905</v>
+        <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>90</v>
+        <v>88368635</v>
       </c>
       <c r="F23" t="n">
         <v>533.99</v>
@@ -1238,11 +1266,14 @@
       <c r="G23" t="n">
         <v>297.13</v>
       </c>
-      <c r="H23" t="n">
-        <v>0</v>
+      <c r="H23" s="2" t="n">
+        <v>45629</v>
       </c>
       <c r="I23" t="n">
-        <v>4151.30657849905</v>
+        <v>0</v>
+      </c>
+      <c r="J23" t="n">
+        <v>4061.30657849905</v>
       </c>
     </row>
     <row r="24">
@@ -1253,19 +1284,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>096.859.725-XX</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>R&amp;D</t>
-        </is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>1362.231969577253</v>
       </c>
       <c r="D24" t="n">
-        <v>1362.231969577253</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>90</v>
+        <v>88368636</v>
       </c>
       <c r="F24" t="n">
         <v>444.99</v>
@@ -1273,11 +1302,14 @@
       <c r="G24" t="n">
         <v>297.13</v>
       </c>
-      <c r="H24" t="n">
-        <v>0</v>
+      <c r="H24" s="2" t="n">
+        <v>45583</v>
       </c>
       <c r="I24" t="n">
-        <v>2194.351969577253</v>
+        <v>0</v>
+      </c>
+      <c r="J24" t="n">
+        <v>2104.351969577253</v>
       </c>
     </row>
     <row r="25">
@@ -1288,19 +1320,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>417.960.836-XX</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>R&amp;D</t>
-        </is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>7920.453739691342</v>
       </c>
       <c r="D25" t="n">
-        <v>7920.453739691342</v>
+        <v>116.57</v>
       </c>
       <c r="E25" t="n">
-        <v>206.57</v>
+        <v>88386531</v>
       </c>
       <c r="F25" t="n">
         <v>364.76</v>
@@ -1308,11 +1338,14 @@
       <c r="G25" t="n">
         <v>297.13</v>
       </c>
-      <c r="H25" t="n">
+      <c r="H25" s="2" t="n">
+        <v>45510</v>
+      </c>
+      <c r="I25" t="n">
         <v>141.46</v>
       </c>
-      <c r="I25" t="n">
-        <v>8930.37373969134</v>
+      <c r="J25" t="n">
+        <v>8840.37373969134</v>
       </c>
     </row>
     <row r="26">
@@ -1323,19 +1356,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>738.071.947-XX</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>R&amp;D</t>
-        </is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>6387.293051889353</v>
       </c>
       <c r="D26" t="n">
-        <v>6387.293051889353</v>
+        <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>90</v>
+        <v>88390114</v>
       </c>
       <c r="F26" t="n">
         <v>364.76</v>
@@ -1343,11 +1374,14 @@
       <c r="G26" t="n">
         <v>297.13</v>
       </c>
-      <c r="H26" t="n">
-        <v>0</v>
+      <c r="H26" s="2" t="n">
+        <v>45618</v>
       </c>
       <c r="I26" t="n">
-        <v>7139.183051889353</v>
+        <v>0</v>
+      </c>
+      <c r="J26" t="n">
+        <v>7049.183051889353</v>
       </c>
     </row>
     <row r="27">
@@ -1358,19 +1392,17 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>159.182.058-XX</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
           <t>COGS</t>
         </is>
       </c>
+      <c r="C27" t="n">
+        <v>6015.101383248207</v>
+      </c>
       <c r="D27" t="n">
-        <v>6015.101383248207</v>
+        <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>90</v>
+        <v>88420860</v>
       </c>
       <c r="F27" t="n">
         <v>364.76</v>
@@ -1378,11 +1410,14 @@
       <c r="G27" t="n">
         <v>297.13</v>
       </c>
-      <c r="H27" t="n">
+      <c r="H27" s="2" t="n">
+        <v>45680</v>
+      </c>
+      <c r="I27" t="n">
         <v>254.63</v>
       </c>
-      <c r="I27" t="n">
-        <v>7021.621383248207</v>
+      <c r="J27" t="n">
+        <v>6931.621383248207</v>
       </c>
     </row>
     <row r="28">
@@ -1393,19 +1428,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>580.293.169-XX</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
           <t>COGS</t>
         </is>
       </c>
+      <c r="C28" t="n">
+        <v>7266.55679736717</v>
+      </c>
       <c r="D28" t="n">
-        <v>7266.55679736717</v>
+        <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>90</v>
+        <v>88966105</v>
       </c>
       <c r="F28" t="n">
         <v>533.99</v>
@@ -1413,11 +1446,14 @@
       <c r="G28" t="n">
         <v>297.13</v>
       </c>
-      <c r="H28" t="n">
+      <c r="H28" s="2" t="n">
+        <v>44895</v>
+      </c>
+      <c r="I28" t="n">
         <v>254.63</v>
       </c>
-      <c r="I28" t="n">
-        <v>8442.30679736717</v>
+      <c r="J28" t="n">
+        <v>8352.30679736717</v>
       </c>
     </row>
     <row r="29">
@@ -1428,19 +1464,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>201.304.270-XX</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>R&amp;D</t>
-        </is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>4610.394047610112</v>
       </c>
       <c r="D29" t="n">
-        <v>4610.394047610112</v>
+        <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>90</v>
+        <v>89166266</v>
       </c>
       <c r="F29" t="n">
         <v>364.76</v>
@@ -1448,11 +1482,14 @@
       <c r="G29" t="n">
         <v>297.13</v>
       </c>
-      <c r="H29" t="n">
+      <c r="H29" s="2" t="n">
+        <v>45343</v>
+      </c>
+      <c r="I29" t="n">
         <v>254.63</v>
       </c>
-      <c r="I29" t="n">
-        <v>5616.914047610113</v>
+      <c r="J29" t="n">
+        <v>5526.914047610113</v>
       </c>
     </row>
     <row r="30">
@@ -1463,19 +1500,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>344.637.503-XX</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>R&amp;D</t>
-        </is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>4587.767886848967</v>
       </c>
       <c r="D30" t="n">
-        <v>4587.767886848967</v>
+        <v>27</v>
       </c>
       <c r="E30" t="n">
-        <v>117</v>
+        <v>88111709</v>
       </c>
       <c r="F30" t="n">
         <v>364.76</v>
@@ -1483,11 +1518,14 @@
       <c r="G30" t="n">
         <v>297.13</v>
       </c>
-      <c r="H30" t="n">
-        <v>0</v>
+      <c r="H30" s="2" t="n">
+        <v>44704</v>
       </c>
       <c r="I30" t="n">
-        <v>5366.657886848967</v>
+        <v>0</v>
+      </c>
+      <c r="J30" t="n">
+        <v>5276.657886848967</v>
       </c>
     </row>
     <row r="31">
@@ -1498,19 +1536,17 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>622.415.381-XX</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
           <t>COGS</t>
         </is>
       </c>
+      <c r="C31" t="n">
+        <v>8187.839600815882</v>
+      </c>
       <c r="D31" t="n">
-        <v>8187.839600815882</v>
+        <v>156</v>
       </c>
       <c r="E31" t="n">
-        <v>246</v>
+        <v>89325373</v>
       </c>
       <c r="F31" t="n">
         <v>364.76</v>
@@ -1518,11 +1554,14 @@
       <c r="G31" t="n">
         <v>297.13</v>
       </c>
-      <c r="H31" t="n">
+      <c r="H31" s="2" t="n">
+        <v>45681</v>
+      </c>
+      <c r="I31" t="n">
         <v>254.63</v>
       </c>
-      <c r="I31" t="n">
-        <v>9350.35960081588</v>
+      <c r="J31" t="n">
+        <v>9260.35960081588</v>
       </c>
     </row>
     <row r="32">
@@ -1533,19 +1572,17 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>943.526.492-XX</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>R&amp;D</t>
-        </is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>1280.596453813949</v>
       </c>
       <c r="D32" t="n">
-        <v>1280.596453813949</v>
+        <v>0</v>
       </c>
       <c r="E32" t="n">
-        <v>90</v>
+        <v>89345506</v>
       </c>
       <c r="F32" t="n">
         <v>444.99</v>
@@ -1553,11 +1590,14 @@
       <c r="G32" t="n">
         <v>297.13</v>
       </c>
-      <c r="H32" t="n">
+      <c r="H32" s="2" t="n">
+        <v>45378</v>
+      </c>
+      <c r="I32" t="n">
         <v>254.63</v>
       </c>
-      <c r="I32" t="n">
-        <v>2367.346453813949</v>
+      <c r="J32" t="n">
+        <v>2277.346453813949</v>
       </c>
     </row>
     <row r="33">
@@ -1568,19 +1608,17 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>364.637.503-XX</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>R&amp;D</t>
-        </is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>8837.775201541868</v>
       </c>
       <c r="D33" t="n">
-        <v>8837.775201541868</v>
+        <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>90</v>
+        <v>89440769</v>
       </c>
       <c r="F33" t="n">
         <v>364.76</v>
@@ -1588,11 +1626,14 @@
       <c r="G33" t="n">
         <v>297.13</v>
       </c>
-      <c r="H33" t="n">
+      <c r="H33" s="2" t="n">
+        <v>45383</v>
+      </c>
+      <c r="I33" t="n">
         <v>254.63</v>
       </c>
-      <c r="I33" t="n">
-        <v>9844.295201541867</v>
+      <c r="J33" t="n">
+        <v>9754.295201541867</v>
       </c>
     </row>
     <row r="34">
@@ -1603,19 +1644,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>695.748.614-XX</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>R&amp;D</t>
-        </is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>3266.657357480083</v>
       </c>
       <c r="D34" t="n">
-        <v>3266.657357480083</v>
+        <v>74</v>
       </c>
       <c r="E34" t="n">
-        <v>164</v>
+        <v>89454088</v>
       </c>
       <c r="F34" t="n">
         <v>364.76</v>
@@ -1623,11 +1662,14 @@
       <c r="G34" t="n">
         <v>297.13</v>
       </c>
-      <c r="H34" t="n">
-        <v>0</v>
+      <c r="H34" s="2" t="n">
+        <v>45552</v>
       </c>
       <c r="I34" t="n">
-        <v>4092.547357480083</v>
+        <v>0</v>
+      </c>
+      <c r="J34" t="n">
+        <v>4002.547357480083</v>
       </c>
     </row>
     <row r="35">
@@ -1638,19 +1680,17 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>437.960.836-XX</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>R&amp;D</t>
-        </is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>3490.64446620121</v>
       </c>
       <c r="D35" t="n">
-        <v>3490.64446620121</v>
+        <v>0</v>
       </c>
       <c r="E35" t="n">
-        <v>90</v>
+        <v>89481833</v>
       </c>
       <c r="F35" t="n">
         <v>444.99</v>
@@ -1658,11 +1698,14 @@
       <c r="G35" t="n">
         <v>297.13</v>
       </c>
-      <c r="H35" t="n">
-        <v>0</v>
+      <c r="H35" s="2" t="n">
+        <v>45644</v>
       </c>
       <c r="I35" t="n">
-        <v>4322.76446620121</v>
+        <v>0</v>
+      </c>
+      <c r="J35" t="n">
+        <v>4232.76446620121</v>
       </c>
     </row>
     <row r="36">
@@ -1673,19 +1716,17 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>179.182.058-XX</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
           <t>COGS</t>
         </is>
       </c>
+      <c r="C36" t="n">
+        <v>257.9421561647101</v>
+      </c>
       <c r="D36" t="n">
-        <v>257.9421561647101</v>
+        <v>0</v>
       </c>
       <c r="E36" t="n">
-        <v>90</v>
+        <v>89587095</v>
       </c>
       <c r="F36" t="n">
         <v>404.91</v>
@@ -1693,11 +1734,14 @@
       <c r="G36" t="n">
         <v>297.13</v>
       </c>
-      <c r="H36" t="n">
+      <c r="H36" s="2" t="n">
+        <v>45057</v>
+      </c>
+      <c r="I36" t="n">
         <v>254.63</v>
       </c>
-      <c r="I36" t="n">
-        <v>1304.61215616471</v>
+      <c r="J36" t="n">
+        <v>1214.61215616471</v>
       </c>
     </row>
     <row r="37">
@@ -1708,19 +1752,17 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>221.304.270-XX</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>R&amp;D</t>
-        </is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>9925.179313508823</v>
       </c>
       <c r="D37" t="n">
-        <v>9925.179313508823</v>
+        <v>642</v>
       </c>
       <c r="E37" t="n">
-        <v>732</v>
+        <v>89949426</v>
       </c>
       <c r="F37" t="n">
         <v>364.76</v>
@@ -1728,11 +1770,14 @@
       <c r="G37" t="n">
         <v>297.13</v>
       </c>
-      <c r="H37" t="n">
+      <c r="H37" s="2" t="n">
+        <v>45624</v>
+      </c>
+      <c r="I37" t="n">
         <v>254.63</v>
       </c>
-      <c r="I37" t="n">
-        <v>11573.69931350882</v>
+      <c r="J37" t="n">
+        <v>11483.69931350882</v>
       </c>
     </row>
     <row r="38">
@@ -1743,19 +1788,17 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>642.415.381-XX</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
           <t>COGS</t>
         </is>
       </c>
+      <c r="C38" t="n">
+        <v>3997.081814681696</v>
+      </c>
       <c r="D38" t="n">
-        <v>3997.081814681696</v>
+        <v>0</v>
       </c>
       <c r="E38" t="n">
-        <v>90</v>
+        <v>89980842</v>
       </c>
       <c r="F38" t="n">
         <v>444.99</v>
@@ -1763,11 +1806,14 @@
       <c r="G38" t="n">
         <v>297.13</v>
       </c>
-      <c r="H38" t="n">
-        <v>0</v>
+      <c r="H38" s="2" t="n">
+        <v>45163</v>
       </c>
       <c r="I38" t="n">
-        <v>4829.201814681695</v>
+        <v>0</v>
+      </c>
+      <c r="J38" t="n">
+        <v>4739.201814681695</v>
       </c>
     </row>
     <row r="39">
@@ -1778,19 +1824,17 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>963.526.492-XX</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>R&amp;D</t>
-        </is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>5244.95395791246</v>
       </c>
       <c r="D39" t="n">
-        <v>5244.95395791246</v>
+        <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>90</v>
+        <v>92660401</v>
       </c>
       <c r="F39" t="n">
         <v>533.99</v>
@@ -1798,11 +1842,14 @@
       <c r="G39" t="n">
         <v>297.13</v>
       </c>
-      <c r="H39" t="n">
-        <v>0</v>
+      <c r="H39" s="2" t="n">
+        <v>45687</v>
       </c>
       <c r="I39" t="n">
-        <v>6166.07395791246</v>
+        <v>0</v>
+      </c>
+      <c r="J39" t="n">
+        <v>6076.07395791246</v>
       </c>
     </row>
     <row r="40">
@@ -1813,19 +1860,17 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>384.637.503-XX</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>R&amp;D</t>
-        </is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>6183.77422031294</v>
       </c>
       <c r="D40" t="n">
-        <v>6183.77422031294</v>
+        <v>0</v>
       </c>
       <c r="E40" t="n">
-        <v>90</v>
+        <v>92706063</v>
       </c>
       <c r="F40" t="n">
         <v>364.76</v>
@@ -1833,11 +1878,14 @@
       <c r="G40" t="n">
         <v>297.13</v>
       </c>
-      <c r="H40" t="n">
-        <v>0</v>
+      <c r="H40" s="2" t="n">
+        <v>45603</v>
       </c>
       <c r="I40" t="n">
-        <v>6935.66422031294</v>
+        <v>0</v>
+      </c>
+      <c r="J40" t="n">
+        <v>6845.66422031294</v>
       </c>
     </row>
     <row r="41">
@@ -1848,19 +1896,17 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>016.859.725-XX</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>R&amp;D</t>
-        </is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>8497.845668097971</v>
       </c>
       <c r="D41" t="n">
-        <v>8497.845668097971</v>
+        <v>0</v>
       </c>
       <c r="E41" t="n">
-        <v>90</v>
+        <v>89470755</v>
       </c>
       <c r="F41" t="n">
         <v>364.76</v>
@@ -1868,11 +1914,14 @@
       <c r="G41" t="n">
         <v>297.13</v>
       </c>
-      <c r="H41" t="n">
+      <c r="H41" s="2" t="n">
+        <v>44894</v>
+      </c>
+      <c r="I41" t="n">
         <v>141.46</v>
       </c>
-      <c r="I41" t="n">
-        <v>9391.195668097969</v>
+      <c r="J41" t="n">
+        <v>9301.195668097969</v>
       </c>
     </row>
     <row r="42">
@@ -1883,19 +1932,17 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>758.071.947-XX</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>R&amp;D</t>
-        </is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>1212.167158944151</v>
       </c>
       <c r="D42" t="n">
-        <v>1212.167158944151</v>
+        <v>0</v>
       </c>
       <c r="E42" t="n">
-        <v>90</v>
+        <v>89481835</v>
       </c>
       <c r="F42" t="n">
         <v>364.76</v>
@@ -1903,11 +1950,14 @@
       <c r="G42" t="n">
         <v>297.13</v>
       </c>
-      <c r="H42" t="n">
-        <v>0</v>
+      <c r="H42" s="2" t="n">
+        <v>45548</v>
       </c>
       <c r="I42" t="n">
-        <v>1964.057158944151</v>
+        <v>0</v>
+      </c>
+      <c r="J42" t="n">
+        <v>1874.057158944151</v>
       </c>
     </row>
     <row r="43">
@@ -1918,19 +1968,17 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>500.293.169-XX</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>R&amp;D</t>
-        </is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>5902.434171124831</v>
       </c>
       <c r="D43" t="n">
-        <v>5902.434171124831</v>
+        <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>90</v>
+        <v>89587095</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -1938,11 +1986,14 @@
       <c r="G43" t="n">
         <v>297.13</v>
       </c>
-      <c r="H43" t="n">
-        <v>0</v>
+      <c r="H43" s="2" t="n">
+        <v>44771</v>
       </c>
       <c r="I43" t="n">
-        <v>6289.564171124831</v>
+        <v>0</v>
+      </c>
+      <c r="J43" t="n">
+        <v>6199.564171124831</v>
       </c>
     </row>
     <row r="44">
@@ -1953,19 +2004,17 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>705.748.614-XX</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>R&amp;D</t>
-        </is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>6173.403303137569</v>
       </c>
       <c r="D44" t="n">
-        <v>6173.403303137569</v>
+        <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>90</v>
+        <v>92763257</v>
       </c>
       <c r="F44" t="n">
         <v>444.99</v>
@@ -1973,11 +2022,14 @@
       <c r="G44" t="n">
         <v>297.13</v>
       </c>
-      <c r="H44" t="n">
-        <v>0</v>
+      <c r="H44" s="2" t="n">
+        <v>45526</v>
       </c>
       <c r="I44" t="n">
-        <v>7005.523303137569</v>
+        <v>0</v>
+      </c>
+      <c r="J44" t="n">
+        <v>6915.523303137569</v>
       </c>
     </row>
     <row r="45">
@@ -1988,19 +2040,17 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>026.859.725-XX</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
           <t>COGS</t>
         </is>
       </c>
+      <c r="C45" t="n">
+        <v>7065.151216079629</v>
+      </c>
       <c r="D45" t="n">
-        <v>7065.151216079629</v>
+        <v>0</v>
       </c>
       <c r="E45" t="n">
-        <v>90</v>
+        <v>92856936</v>
       </c>
       <c r="F45" t="n">
         <v>684.63</v>
@@ -2008,11 +2058,14 @@
       <c r="G45" t="n">
         <v>297.13</v>
       </c>
-      <c r="H45" t="n">
-        <v>0</v>
+      <c r="H45" s="2" t="n">
+        <v>44704</v>
       </c>
       <c r="I45" t="n">
-        <v>8136.911216079629</v>
+        <v>0</v>
+      </c>
+      <c r="J45" t="n">
+        <v>8046.911216079629</v>
       </c>
     </row>
     <row r="46">
@@ -2023,19 +2076,17 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>447.960.836-XX</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>R&amp;D</t>
-        </is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>9095.090151715545</v>
       </c>
       <c r="D46" t="n">
-        <v>9095.090151715545</v>
+        <v>0</v>
       </c>
       <c r="E46" t="n">
-        <v>90</v>
+        <v>92984603</v>
       </c>
       <c r="F46" t="n">
         <v>855.8</v>
@@ -2043,11 +2094,14 @@
       <c r="G46" t="n">
         <v>297.13</v>
       </c>
-      <c r="H46" t="n">
-        <v>0</v>
+      <c r="H46" s="2" t="n">
+        <v>45517</v>
       </c>
       <c r="I46" t="n">
-        <v>10338.02015171554</v>
+        <v>0</v>
+      </c>
+      <c r="J46" t="n">
+        <v>10248.02015171554</v>
       </c>
     </row>
     <row r="47">
@@ -2058,19 +2112,17 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>768.071.947-XX</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>R&amp;D</t>
-        </is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>746.9510783679258</v>
       </c>
       <c r="D47" t="n">
-        <v>746.9510783679258</v>
+        <v>0</v>
       </c>
       <c r="E47" t="n">
-        <v>90</v>
+        <v>93007042</v>
       </c>
       <c r="F47" t="n">
         <v>560.7</v>
@@ -2078,11 +2130,14 @@
       <c r="G47" t="n">
         <v>297.13</v>
       </c>
-      <c r="H47" t="n">
+      <c r="H47" s="2" t="n">
+        <v>45624</v>
+      </c>
+      <c r="I47" t="n">
         <v>254.63</v>
       </c>
-      <c r="I47" t="n">
-        <v>1949.411078367926</v>
+      <c r="J47" t="n">
+        <v>1859.411078367926</v>
       </c>
     </row>
     <row r="48">
@@ -2093,19 +2148,17 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>510.293.169-XX</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
           <t>G&amp;A</t>
         </is>
       </c>
+      <c r="C48" t="n">
+        <v>3952.204962932551</v>
+      </c>
       <c r="D48" t="n">
-        <v>3952.204962932551</v>
+        <v>74</v>
       </c>
       <c r="E48" t="n">
-        <v>164</v>
+        <v>93022264</v>
       </c>
       <c r="F48" t="n">
         <v>364.76</v>
@@ -2113,11 +2166,14 @@
       <c r="G48" t="n">
         <v>297.13</v>
       </c>
-      <c r="H48" t="n">
+      <c r="H48" s="2" t="n">
+        <v>44780</v>
+      </c>
+      <c r="I48" t="n">
         <v>254.63</v>
       </c>
-      <c r="I48" t="n">
-        <v>5032.724962932551</v>
+      <c r="J48" t="n">
+        <v>4942.724962932551</v>
       </c>
     </row>
     <row r="49">
@@ -2128,19 +2184,17 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>231.304.270-XX</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>R&amp;D</t>
-        </is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>6993.13850131002</v>
       </c>
       <c r="D49" t="n">
-        <v>6993.13850131002</v>
+        <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>90</v>
+        <v>93046165</v>
       </c>
       <c r="F49" t="n">
         <v>-328.28</v>
@@ -2148,11 +2202,14 @@
       <c r="G49" t="n">
         <v>297.13</v>
       </c>
-      <c r="H49" t="n">
-        <v>0</v>
+      <c r="H49" s="2" t="n">
+        <v>45465</v>
       </c>
       <c r="I49" t="n">
-        <v>7051.98850131002</v>
+        <v>0</v>
+      </c>
+      <c r="J49" t="n">
+        <v>6961.98850131002</v>
       </c>
     </row>
     <row r="50">
@@ -2163,19 +2220,17 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>652.415.381-XX</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
           <t>G&amp;A</t>
         </is>
       </c>
+      <c r="C50" t="n">
+        <v>490.174359132607</v>
+      </c>
       <c r="D50" t="n">
-        <v>490.174359132607</v>
+        <v>0</v>
       </c>
       <c r="E50" t="n">
-        <v>90</v>
+        <v>93046166</v>
       </c>
       <c r="F50" t="n">
         <v>622.41</v>
@@ -2183,11 +2238,14 @@
       <c r="G50" t="n">
         <v>297.13</v>
       </c>
-      <c r="H50" t="n">
+      <c r="H50" s="2" t="n">
+        <v>45553</v>
+      </c>
+      <c r="I50" t="n">
         <v>254.63</v>
       </c>
-      <c r="I50" t="n">
-        <v>1754.344359132607</v>
+      <c r="J50" t="n">
+        <v>1664.344359132607</v>
       </c>
     </row>
     <row r="51">
@@ -2198,19 +2256,17 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>973.526.492-XX</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>R&amp;D</t>
-        </is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>1461.243910515265</v>
       </c>
       <c r="D51" t="n">
-        <v>1461.243910515265</v>
+        <v>0</v>
       </c>
       <c r="E51" t="n">
-        <v>90</v>
+        <v>93046167</v>
       </c>
       <c r="F51" t="n">
         <v>444.99</v>
@@ -2218,11 +2274,14 @@
       <c r="G51" t="n">
         <v>297.13</v>
       </c>
-      <c r="H51" t="n">
-        <v>0</v>
+      <c r="H51" s="2" t="n">
+        <v>44693</v>
       </c>
       <c r="I51" t="n">
-        <v>2293.363910515265</v>
+        <v>0</v>
+      </c>
+      <c r="J51" t="n">
+        <v>2203.363910515265</v>
       </c>
     </row>
     <row r="52">
@@ -2233,19 +2292,17 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>394.637.503-XX</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
           <t>COGS</t>
         </is>
       </c>
+      <c r="C52" t="n">
+        <v>2741.365342728207</v>
+      </c>
       <c r="D52" t="n">
-        <v>2741.365342728207</v>
+        <v>0</v>
       </c>
       <c r="E52" t="n">
-        <v>90</v>
+        <v>93054920</v>
       </c>
       <c r="F52" t="n">
         <v>444.99</v>
@@ -2253,11 +2310,14 @@
       <c r="G52" t="n">
         <v>297.13</v>
       </c>
-      <c r="H52" t="n">
-        <v>0</v>
+      <c r="H52" s="2" t="n">
+        <v>44894</v>
       </c>
       <c r="I52" t="n">
-        <v>3573.485342728207</v>
+        <v>0</v>
+      </c>
+      <c r="J52" t="n">
+        <v>3483.485342728207</v>
       </c>
     </row>
     <row r="53">
@@ -2268,19 +2328,17 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>189.182.058-XX</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
           <t>COGS</t>
         </is>
       </c>
+      <c r="C53" t="n">
+        <v>8733.661290965678</v>
+      </c>
       <c r="D53" t="n">
-        <v>8733.661290965678</v>
+        <v>0</v>
       </c>
       <c r="E53" t="n">
-        <v>90</v>
+        <v>93007043</v>
       </c>
       <c r="F53" t="n">
         <v>855.8</v>
@@ -2288,11 +2346,14 @@
       <c r="G53" t="n">
         <v>297.13</v>
       </c>
-      <c r="H53" t="n">
+      <c r="H53" s="2" t="n">
+        <v>44693</v>
+      </c>
+      <c r="I53" t="n">
         <v>254.63</v>
       </c>
-      <c r="I53" t="n">
-        <v>10231.22129096568</v>
+      <c r="J53" t="n">
+        <v>10141.22129096568</v>
       </c>
     </row>
     <row r="54">
@@ -2303,19 +2364,17 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>715.748.614-XX</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>R&amp;D</t>
-        </is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>4455.059040524839</v>
       </c>
       <c r="D54" t="n">
-        <v>4455.059040524839</v>
+        <v>0</v>
       </c>
       <c r="E54" t="n">
-        <v>90</v>
+        <v>93379773</v>
       </c>
       <c r="F54" t="n">
         <v>444.99</v>
@@ -2323,11 +2382,14 @@
       <c r="G54" t="n">
         <v>297.13</v>
       </c>
-      <c r="H54" t="n">
-        <v>0</v>
+      <c r="H54" s="2" t="n">
+        <v>45069</v>
       </c>
       <c r="I54" t="n">
-        <v>5287.179040524838</v>
+        <v>0</v>
+      </c>
+      <c r="J54" t="n">
+        <v>5197.179040524838</v>
       </c>
     </row>
     <row r="55">
@@ -2338,19 +2400,17 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>036.859.725-XX</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
           <t>COGS</t>
         </is>
       </c>
+      <c r="C55" t="n">
+        <v>800.1804264146962</v>
+      </c>
       <c r="D55" t="n">
-        <v>800.1804264146962</v>
+        <v>0</v>
       </c>
       <c r="E55" t="n">
-        <v>90</v>
+        <v>93430742</v>
       </c>
       <c r="F55" t="n">
         <v>364.76</v>
@@ -2358,11 +2418,14 @@
       <c r="G55" t="n">
         <v>297.13</v>
       </c>
-      <c r="H55" t="n">
+      <c r="H55" s="2" t="n">
+        <v>45021</v>
+      </c>
+      <c r="I55" t="n">
         <v>254.63</v>
       </c>
-      <c r="I55" t="n">
-        <v>1806.700426414696</v>
+      <c r="J55" t="n">
+        <v>1716.700426414696</v>
       </c>
     </row>
     <row r="56">
@@ -2373,19 +2436,17 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>457.960.836-XX</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>R&amp;D</t>
-        </is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>7336.902571199591</v>
       </c>
       <c r="D56" t="n">
-        <v>7336.902571199591</v>
+        <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>90</v>
+        <v>93551845</v>
       </c>
       <c r="F56" t="n">
         <v>364.76</v>
@@ -2393,11 +2454,14 @@
       <c r="G56" t="n">
         <v>297.13</v>
       </c>
-      <c r="H56" t="n">
-        <v>0</v>
+      <c r="H56" s="2" t="n">
+        <v>45510</v>
       </c>
       <c r="I56" t="n">
-        <v>8088.792571199591</v>
+        <v>0</v>
+      </c>
+      <c r="J56" t="n">
+        <v>7998.792571199591</v>
       </c>
     </row>
     <row r="57">
@@ -2408,19 +2472,17 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>778.071.947-XX</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>R&amp;D</t>
-        </is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>1728.629771639805</v>
       </c>
       <c r="D57" t="n">
-        <v>1728.629771639805</v>
+        <v>27</v>
       </c>
       <c r="E57" t="n">
-        <v>117</v>
+        <v>93551846</v>
       </c>
       <c r="F57" t="n">
         <v>560.7</v>
@@ -2428,11 +2490,14 @@
       <c r="G57" t="n">
         <v>297.13</v>
       </c>
-      <c r="H57" t="n">
-        <v>0</v>
+      <c r="H57" s="2" t="n">
+        <v>45672</v>
       </c>
       <c r="I57" t="n">
-        <v>2703.459771639805</v>
+        <v>0</v>
+      </c>
+      <c r="J57" t="n">
+        <v>2613.459771639805</v>
       </c>
     </row>
     <row r="58">
@@ -2443,19 +2508,17 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>199.182.058-XX</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>R&amp;D</t>
-        </is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>5960.861253655476</v>
       </c>
       <c r="D58" t="n">
-        <v>5960.861253655476</v>
+        <v>0</v>
       </c>
       <c r="E58" t="n">
-        <v>90</v>
+        <v>93824710</v>
       </c>
       <c r="F58" t="n">
         <v>533.99</v>
@@ -2463,11 +2526,14 @@
       <c r="G58" t="n">
         <v>297.13</v>
       </c>
-      <c r="H58" t="n">
+      <c r="H58" s="2" t="n">
+        <v>44720</v>
+      </c>
+      <c r="I58" t="n">
         <v>254.63</v>
       </c>
-      <c r="I58" t="n">
-        <v>7136.611253655476</v>
+      <c r="J58" t="n">
+        <v>7046.611253655476</v>
       </c>
     </row>
     <row r="59">
@@ -2478,19 +2544,17 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>845.601.337-XX</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
           <t>COGS</t>
         </is>
       </c>
+      <c r="C59" t="n">
+        <v>4055.50889721234</v>
+      </c>
       <c r="D59" t="n">
-        <v>4055.50889721234</v>
+        <v>0</v>
       </c>
       <c r="E59" t="n">
-        <v>90</v>
+        <v>94053536</v>
       </c>
       <c r="F59" t="n">
         <v>533.99</v>
@@ -2498,11 +2562,14 @@
       <c r="G59" t="n">
         <v>297.13</v>
       </c>
-      <c r="H59" t="n">
+      <c r="H59" s="2" t="n">
+        <v>45426</v>
+      </c>
+      <c r="I59" t="n">
         <v>254.63</v>
       </c>
-      <c r="I59" t="n">
-        <v>5231.258897212339</v>
+      <c r="J59" t="n">
+        <v>5141.25889721234</v>
       </c>
     </row>
     <row r="60">
@@ -2513,19 +2580,17 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>520.293.169-XX</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>R&amp;D</t>
-        </is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>7306.398876912478</v>
       </c>
       <c r="D60" t="n">
-        <v>7306.398876912478</v>
+        <v>0</v>
       </c>
       <c r="E60" t="n">
-        <v>90</v>
+        <v>94053536</v>
       </c>
       <c r="F60" t="n">
         <v>-17.8</v>
@@ -2533,11 +2598,14 @@
       <c r="G60" t="n">
         <v>297.13</v>
       </c>
-      <c r="H60" t="n">
-        <v>0</v>
+      <c r="H60" s="2" t="n">
+        <v>45327</v>
       </c>
       <c r="I60" t="n">
-        <v>7675.728876912478</v>
+        <v>0</v>
+      </c>
+      <c r="J60" t="n">
+        <v>7585.728876912478</v>
       </c>
     </row>
     <row r="61">
@@ -2548,19 +2616,17 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>112.233.554-XX</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>R&amp;D</t>
-        </is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>6715.641722399166</v>
       </c>
       <c r="D61" t="n">
-        <v>6715.641722399166</v>
+        <v>0</v>
       </c>
       <c r="E61" t="n">
-        <v>90</v>
+        <v>94053536</v>
       </c>
       <c r="F61" t="n">
         <v>498.39</v>
@@ -2568,11 +2634,14 @@
       <c r="G61" t="n">
         <v>297.13</v>
       </c>
-      <c r="H61" t="n">
+      <c r="H61" s="2" t="n">
+        <v>44713</v>
+      </c>
+      <c r="I61" t="n">
         <v>254.63</v>
       </c>
-      <c r="I61" t="n">
-        <v>7855.791722399166</v>
+      <c r="J61" t="n">
+        <v>7765.791722399166</v>
       </c>
     </row>
     <row r="62">
@@ -2583,19 +2652,17 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>740.293.169-XX</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>R&amp;D</t>
-        </is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>1223.312552727439</v>
       </c>
       <c r="D62" t="n">
-        <v>1223.312552727439</v>
+        <v>0</v>
       </c>
       <c r="E62" t="n">
-        <v>90</v>
+        <v>83726851</v>
       </c>
       <c r="F62" t="n">
         <v>533.99</v>
@@ -2603,11 +2670,14 @@
       <c r="G62" t="n">
         <v>297.13</v>
       </c>
-      <c r="H62" t="n">
+      <c r="H62" s="2" t="n">
+        <v>45670</v>
+      </c>
+      <c r="I62" t="n">
         <v>254.63</v>
       </c>
-      <c r="I62" t="n">
-        <v>2399.062552727439</v>
+      <c r="J62" t="n">
+        <v>2309.062552727439</v>
       </c>
     </row>
     <row r="63">
@@ -2618,19 +2688,17 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>757.960.836-XX</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
           <t>COGS</t>
         </is>
       </c>
+      <c r="C63" t="n">
+        <v>2036.514997025348</v>
+      </c>
       <c r="D63" t="n">
-        <v>2036.514997025348</v>
+        <v>0</v>
       </c>
       <c r="E63" t="n">
-        <v>90</v>
+        <v>84863695</v>
       </c>
       <c r="F63" t="n">
         <v>364.76</v>
@@ -2638,11 +2706,14 @@
       <c r="G63" t="n">
         <v>297.13</v>
       </c>
-      <c r="H63" t="n">
-        <v>0</v>
+      <c r="H63" s="2" t="n">
+        <v>45398</v>
       </c>
       <c r="I63" t="n">
-        <v>2788.404997025348</v>
+        <v>0</v>
+      </c>
+      <c r="J63" t="n">
+        <v>2698.404997025348</v>
       </c>
     </row>
   </sheetData>
